--- a/artfynd/A 35054-2026 artfynd.xlsx
+++ b/artfynd/A 35054-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137234111</v>
       </c>
       <c r="B2" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35054-2026 artfynd.xlsx
+++ b/artfynd/A 35054-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137234111</v>
       </c>
       <c r="B2" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35054-2026 artfynd.xlsx
+++ b/artfynd/A 35054-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137234111</v>
       </c>
       <c r="B2" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35054-2026 artfynd.xlsx
+++ b/artfynd/A 35054-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137234111</v>
       </c>
       <c r="B2" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35054-2026 artfynd.xlsx
+++ b/artfynd/A 35054-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137234111</v>
       </c>
       <c r="B2" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35054-2026 artfynd.xlsx
+++ b/artfynd/A 35054-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137234111</v>
       </c>
       <c r="B2" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35054-2026 artfynd.xlsx
+++ b/artfynd/A 35054-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137234111</v>
       </c>
       <c r="B2" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35054-2026 artfynd.xlsx
+++ b/artfynd/A 35054-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137234111</v>
       </c>
       <c r="B2" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
